--- a/docs/downloads/entra-administrator-checklist.xlsx
+++ b/docs/downloads/entra-administrator-checklist.xlsx
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -546,7 +546,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Role: Entra Global Admin  |  FSI Agent Governance Framework v1.2.41 — February 2026</t>
+          <t>Role: Entra Global Admin  |  FSI Agent Governance Framework v1.3.0 — March 2026</t>
         </is>
       </c>
     </row>
@@ -638,12 +638,12 @@
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Agent Inventory and Metadata Management</t>
+          <t>Entra Agent ID: Identity Governance for Agents</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
@@ -654,10 +654,29 @@
       <c r="D8" s="9" t="n"/>
       <c r="E8" s="11" t="n"/>
     </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>FSI Agent Governance Framework v1.2.41 — February 2026</t>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Agent Inventory and Metadata Management</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="7" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>FSI Agent Governance Framework v1.3.0 — March 2026</t>
         </is>
       </c>
     </row>
@@ -665,11 +684,11 @@
   <autoFilter ref="A4:E4"/>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A11:E11"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="C5:C8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Status" error="Please select: Not Started, In Progress, Completed, or N/A" promptTitle="Status" prompt="Select implementation status" type="list">
+    <dataValidation sqref="C5:C9" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Status" error="Please select: Not Started, In Progress, Completed, or N/A" promptTitle="Status" prompt="Select implementation status" type="list">
       <formula1>"Not Started,In Progress,Completed,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -677,7 +696,7 @@
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;CEntra Administrator Checklist</oddHeader>
-    <oddFooter>&amp;CFSI Agent Governance Framework v1.2.41 — February 2026</oddFooter>
+    <oddFooter>&amp;CFSI Agent Governance Framework v1.3.0 — March 2026</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/docs/downloads/entra-administrator-checklist.xlsx
+++ b/docs/downloads/entra-administrator-checklist.xlsx
@@ -546,7 +546,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Role: Entra Global Admin  |  FSI Agent Governance Framework v1.3.0 — March 2026</t>
+          <t>Role: Entra Global Admin  |  FSI Agent Governance Framework v1.4.0 — April 2026</t>
         </is>
       </c>
     </row>
@@ -673,10 +673,11 @@
       <c r="D9" s="5" t="n"/>
       <c r="E9" s="7" t="n"/>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>FSI Agent Governance Framework v1.3.0 — March 2026</t>
+          <t>FSI Agent Governance Framework v1.4.0 — April 2026</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/entra-administrator-checklist.xlsx
+++ b/docs/downloads/entra-administrator-checklist.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Entra Global Admin" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entra Global Admin" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Entra Global Admin'!$A$4:$E$4</definedName>
@@ -546,7 +546,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Role: Entra Global Admin  |  FSI Agent Governance Framework v1.4.0 — April 2026</t>
+          <t>Role: Entra Global Admin  |  FSI Agent Governance Framework v1.6.2 — May 2026</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Application-Level Authorization and RBAC</t>
+          <t>Application-Level Authorization and Role-Based Access Control (RBAC)</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Entra Agent ID: Identity Governance for Agents</t>
+          <t>Entra Agent ID — Identity Governance for Agents</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
@@ -677,7 +677,7 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>FSI Agent Governance Framework v1.4.0 — April 2026</t>
+          <t>FSI Agent Governance Framework v1.6.2 — May 2026</t>
         </is>
       </c>
     </row>
